--- a/stock_images_data_cloned.xlsx
+++ b/stock_images_data_cloned.xlsx
@@ -436,7 +436,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sky, Sky Clouds, Blue Atmosphere,</t>
+          <t>Clouds, Blue Sky, Atmosphere, Sky</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Subtropical Rainbow, Rainfall, Sea,</t>
+          <t>Subtropical Rainfall, Rainbow, Sea,</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Road, Sakura Japan, Cherry Blossoms,</t>
+          <t>Blossoms, Cherry Road, Sakura Japan,</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Marguerite, Cape Plant Flower,</t>
+          <t>Plant Flower, Marguerite, Cape</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tree Relaxing Under Rest The</t>
+          <t>Relaxing The Under Rest Tree</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rabbit, Cottontail Wild Grass</t>
+          <t>Cottontail Wild Rabbit, Grass</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Crocus, Flowers, Plant Spring,</t>
+          <t>Plant Spring, Crocus, Flowers,</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Drink, Coffee, Vacation, Café, Table</t>
+          <t>Coffee, Drink, Café, Vacation, Table</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fall, Epic, Nature, Light Waterfall,</t>
+          <t>Waterfall, Fall, Light Nature, Epic,</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nature Field, Sunrise, Dawn, Morning,</t>
+          <t>Dawn, Field, Morning, Sunrise, Nature</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Robin, Birdwatching, Bird, Animal</t>
+          <t>Animal Robin, Birdwatching, Bird,</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Spring Soil, Bloom Flowers, Seedlings,</t>
+          <t>Spring Bloom Soil, Flowers, Seedlings,</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hills Road, Countryside, Highway,</t>
+          <t>Road, Hills Countryside, Highway,</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Monochrome, Cityscape, City Bridge,</t>
+          <t>Cityscape, City Bridge, Monochrome,</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Water Spring, Sakura, Cherry Blossoms,</t>
+          <t>Sakura, Cherry Blossoms, Water Spring,</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Eggs, Template, Background, Art Easter,</t>
+          <t>Background, Art Template, Easter, Eggs,</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Indian Species Ornithology, Chat, Bird,</t>
+          <t>Species Chat, Ornithology, Bird, Indian</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Night, Village, Winter, Season Town,</t>
+          <t>Season Night, Village, Town, Winter,</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bloom Flower, Pansy, Viola, Blossom,</t>
+          <t>Blossom, Flower, Bloom Viola, Pansy,</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Architecture, Lake, Port, Vacations</t>
+          <t>Port, Architecture, Vacations Lake,</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Flowers, Sunflowers, Plant</t>
+          <t>Sunflowers, Flowers, Plant</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Spring, Coffee, Flowers, Morning</t>
+          <t>Coffee, Morning Flowers, Spring,</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lake, Peak, Roys Mountains Wanaka,</t>
+          <t>Mountains Wanaka, Roys Lake, Peak,</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Thank many downloads and you, likes. for everyone. you</t>
+          <t>Thank and everyone. many downloads you, likes. for you</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Exploration Beach, Outdoors, Nature,</t>
+          <t>Beach, Outdoors, Exploration Nature,</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>West Danish Jutland. during Shot Coast of sunset. The</t>
+          <t>Jutland. during Shot sunset. The of West Danish Coast</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bird, Penguin, Animal Gentoo</t>
+          <t>Animal Gentoo Penguin, Bird,</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sea, Water, Tree Lantern, Heaven, Beach,</t>
+          <t>Water, Lantern, Heaven, Sea, Beach, Tree</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Spring, Easter, Easter Bunny</t>
+          <t>Easter, Easter Spring, Bunny</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>on green rock during brown lake daytime trees formation</t>
+          <t>during brown trees green formation on lake rock daytime</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tower, Eiffel Tourist Attraction, Travel</t>
+          <t>Attraction, Tower, Tourist Eiffel Travel</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Standing Stones, Menhir, Clouds, Stones</t>
+          <t>Clouds, Standing Stones Stones, Menhir,</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Path Road, Winter, Snow, Trees, Frost,</t>
+          <t>Road, Snow, Trees, Path Winter, Frost,</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bird, Woodpecker</t>
+          <t>Woodpecker Bird,</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tape, Cassette, Classic Retro, Music,</t>
+          <t>Retro, Classic Tape, Cassette, Music,</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Power Energy, Clouds, Wind Mills,</t>
+          <t>Clouds, Power Mills, Wind Energy,</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tartini, Travel, Square, Tourism, Piran</t>
+          <t>Tourism, Square, Tartini, Piran Travel,</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Eggs, Nest, Colored Eggs Easter</t>
+          <t>Nest, Eggs Colored Easter Eggs,</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nature, Winter, Season, Travel Outdoors,</t>
+          <t>Outdoors, Season, Nature, Winter, Travel</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Glacier, Dying Glacier Glaciers, Melting</t>
+          <t>Glaciers, Glacier Glacier, Dying Melting</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Jungle, Nature Tropical, Green, Forest,</t>
+          <t>Forest, Green, Jungle, Tropical, Nature</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Flower, Tulip, Petals Bloom, Blossom,</t>
+          <t>Blossom, Petals Flower, Bloom, Tulip,</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Flowers, Petals Pink</t>
+          <t>Pink Flowers, Petals</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Passiflora, Flower, Passion Flower</t>
+          <t>Flower Flower, Passion Passiflora,</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Blessing Faith, Prayer, Hope, Religion,</t>
+          <t>Religion, Hope, Faith, Prayer, Blessing</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Star, Cosmos Space, Universe, Galaxy,</t>
+          <t>Star, Universe, Galaxy, Cosmos Space,</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Macro Insect, Dragonfly, Nature,</t>
+          <t>Dragonfly, Insect, Macro Nature,</t>
         </is>
       </c>
     </row>
